--- a/원료_지식_확장.xlsx
+++ b/원료_지식_확장.xlsx
@@ -11,7 +11,7 @@
     <sheet name="비율_제형_사다리" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기능성원료'!$A$2:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기능성원료'!$A$2:$F$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F7E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,7 +87,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF7E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E9DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FBE9D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2B3"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -182,6 +217,27 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -190,10 +246,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -561,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -804,9 +860,9 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>유화</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>가용화</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -836,7 +892,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
@@ -868,7 +924,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
@@ -900,7 +956,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
@@ -932,7 +988,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
@@ -964,7 +1020,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
@@ -996,7 +1052,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
@@ -1028,7 +1084,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
@@ -1060,7 +1116,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
@@ -1092,7 +1148,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
@@ -1124,7 +1180,7 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
@@ -1156,7 +1212,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
@@ -1188,7 +1244,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1220,7 +1276,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1252,7 +1308,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1284,7 +1340,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1316,7 +1372,7 @@
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1348,7 +1404,7 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1380,7 +1436,7 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1412,7 +1468,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1444,7 +1500,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
@@ -1476,7 +1532,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>에몰리언트</t>
         </is>
@@ -1508,7 +1564,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>에몰리언트</t>
         </is>
@@ -1540,7 +1596,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>에몰리언트</t>
         </is>
@@ -1572,7 +1628,7 @@
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>에몰리언트</t>
         </is>
@@ -1604,7 +1660,7 @@
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>에몰리언트</t>
         </is>
@@ -1638,69 +1694,3141 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>하이드로제네이티드폴리이소부텐 / C13-15 알케인 (탄화수소)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>1~10%</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>지방산 없는 탄화수소 에몰리언트 — 산패 없고 말라세지아-세이프.</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>스쿠알란</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>과량 시 무겁고 번들. 세이프 팔레트 후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>하이드로제네이티드폴리데센 (Hydrogenated Polydecene)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>합성 탄화수소 오일. 무취·무산패·세이프.</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>스쿠알란</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>미네랄오일 / 페트롤라툼 (Paraffinum Liquidum / Petrolatum)</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>1~15%</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>가장 강한 폐쇄막(수분 증발 차단). 지방산 없음 → 세이프.</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>'천연' 포지션 상충, 무거움. 장벽 손상 피부엔 효과적</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>디카프릴릴카보네이트 (Dicaprylyl Carbonate)</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>매우 빠른 흡수·산뜻 마무리. 선크림 필터 용해.</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>C8 사슬 — 비교적 세이프</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>코코-카프릴레이트/카프레이트 (Coco-Caprylate/Caprate)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>식물유래 경량 에스터. 실리콘 대체감.</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>C8~C10 중심이나 코코넛 유래 혼합 — C12↑ 함량 TDS 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>세틸에틸헥사노에이트 (Cetyl Ethylhexanoate)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>가볍고 산뜻한 범용 에스터(유화제 아님).</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>C16 알코올 에스터 — 말라세지아 회색지대</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>이소노닐이소노나노에이트 (Isononyl Isononanoate)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>2~8%</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>실키한 분지 에스터. 실리콘 대체 촉감.</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>C9 — 비교적 세이프</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>에틸헥실팔미테이트 (Ethylhexyl Palmitate)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>저렴 범용 에스터. 발림·광택.</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>말라세지아 주의(C11~24 지방산 에스터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>옥틸도데칸올 (Octyldodecanol)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>분지 지방알코올. 립·크림 유연, 안료 분산.</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>C20 — 말라세지아 회색지대</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>디이소스테아릴말레이트 (Diisostearyl Malate)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>5~30%</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>립 광택·밀착·안료 분산.</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>피마자유</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>말라세지아 주의(C11~24 지방산 에스터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>에몰리언트</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>콜레스테롤 (Cholesterol)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0.1~1%</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>장벽 지질 3요소(세라마이드:콜레스테롤:지방산).</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>세라마이드와 비율(≈3:1:1) 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>감촉·실리콘</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>디메치콘크로스폴리머 (Dimethicone Crosspolymer)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>1~10%</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>블러링·벨벳 파우더리 감촉(프라이머·크림 마무리).</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>'천연' 포지션 상충</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>감촉·실리콘</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>페닐트리메치콘 (Phenyl Trimethicone)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>광택·윤기. 헤어세럼·립.</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>감촉·실리콘</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>아모다이메치콘 (Amodimethicone)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0.5~3%</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>손상 모발에 선택 흡착하는 컨디셔닝 실리콘.</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>컨디셔너·트리트먼트용</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>감촉·실리콘</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>사이클로펜타실록산 (Cyclopentasiloxane, D5)</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>5~30%</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>휘발 실리콘 — 끈적임 없이 날아가며 실키.</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>헵탄(사탕수수 유래)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>EU는 씻어내는 제품 0.1% 제한 — 수출 시 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>실리카 (Silica)</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>1~10%</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>피지 흡착·매트·블러링. 선크림 끈적임 완화.</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>옥수수전분</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>미세분말 흡입 주의(마스크)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>타피오카전분 (Tapioca Starch)</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>1~10%</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>보송한 마무리·유분감↓.</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>옥수수전분</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>수분 제형에선 미생물 영양원 — 방부 철저</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>카올린 (Kaolin)</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>5~30%</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>가장 순한 화이트 클레이. 흡착·매트.</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>과건조 — 보습제 병용</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>벤토나이트 (Bentonite)</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>5~20%</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>강한 흡착·팽윤 클레이. 지성 팩·점증 보조.</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>금속 도구 피함, 과건조</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>마이카 (Mica)</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>1~20%</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>광택·펄·부드러운 슬립.</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>윤리적 채굴 출처 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>분말</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>보론나이트라이드 (Boron Nitride)</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>1~10%</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>부드러운 슬립·소프트포커스.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>글리세린 (Glycerin)</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>2~8%</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>보습 표준. 3~5%가 끈적임 대비 효율 최적.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>식물성 글리세린</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>8%↑ 끈적·건조 환경 역삼투</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>프로판디올 (Propanediol)</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>2~8%</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>옥수수 유래 폴리올. 글리세린보다 가볍고 방부 보조.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>부틸렌글라이콜 (Butylene Glycol)</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>2~8%</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>가벼운 습윤·용제·방부 보조. 추출물 용매로 흔함.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>프로판디올</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>펜틸렌글라이콜 (Pentylene Glycol)</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>습윤+방부 보조(히어로 v2 사용).</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>고농도 따가움 드묾</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>베타인 (Betaine)</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>사탕무 유래. 끈적임 적고 계면활성제 자극 완화.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>소듐PCA (Sodium PCA)</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>0.5~3%</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>천연보습인자(NMF) 성분. 가볍고 촉촉.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>우레아 (Urea)</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>NMF·각질 연화. 5%↑ 거친 피부·각질.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>민감 피부 따가움. 수용액에서 분해돼 pH 상승 — 소량·단기</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>소듐하이알루로네이트 (Sodium Hyaluronate)</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>0.05~0.5%(분말)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>수분 붙잡음. 고·저분자 섞어 층별 보습.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>분말은 미리 불림. 과량 시 밀림</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>트레할로스 (Trehalose)</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>1~3%</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>보호당 — 건조 스트레스에서 막·단백질 보호.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>폴리글루타믹애씨드 (Polyglutamic Acid)</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>0.05~0.5%</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>강한 보수력·얇은 필름감.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>과량 끈적·밀림</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>알부틴 (Arbutin)</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>2~5%</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>미백 고시 성분(2~5%). 티로시나제 억제.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>고온·고pH에서 분해 — pH 5~7, 냉각상 투입</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>마그네슘아스코빌포스페이트 (MAP)</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>미백 고시(3%). 안정·저자극 비타민C.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>pH 6~7, 산성에서 불안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>아스코빅애씨드 (L-Ascorbic Acid, 순수 비타민C)</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>5~20%</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>가장 강한 비타민C(톤·항산화).</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>pH ≤3.5 필요·산화 빠름 → 무수/에어리스·소량 제조</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>알파-비사보롤 (alpha-Bisabolol)</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.5%</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>진정 + 미백 고시 성분(0.5%).</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>캐모마일추출물</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>유용성감초추출물 (Licorice Root Extract)</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>0.05%(고시)</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>미백 고시·진정.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>고시 농도·원료 규격 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>트라넥사믹애씨드 (Tranexamic Acid)</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>2~3%</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>톤·잡티 케어 원료.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>국내 미백 고시 성분 아님 — '미백' 표방 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>레티닐팔미테이트 (Retinyl Palmitate)</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>고시 10,000IU/g</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>순한 레티노이드 에스터(주름 고시).</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>바쿠치올</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>빛·산소 불안정, 임부 주의, 팔미트산 에스터</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>바쿠치올 (Bakuchiol)</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>0.5~1%</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>식물 유래 레티놀 대체(자극 적음).</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>주름 고시 성분 아님 — 표방 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>아세틸헥사펩타이드-8 (Argireline)</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>2~10%(원료액)</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>표정주름 펩타이드.</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>원료액% ≠ 펩타이드 농도</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>코퍼트라이펩타이드-1 (GHK-Cu)</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>0.5~2%(원료액)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>재생·탄력 펩타이드(푸른색).</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>비타민C·강산·EDTA와 함께 쓰면 불안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>세라마이드NP (Ceramide NP)</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>0.1~1%</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>장벽 지질. 콜레스테롤·지방산과 비율 설계.</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>용해 어려움 — 유상 고온 용해</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>마데카소사이드 (Madecassoside)</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.5%</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>병풀 유래 진정·장벽(보유 원료).</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>병풀추출물</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>병풀추출물 (Centella Asiatica Extract)</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>진정·재생 대표 추출물.</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>추출물마다 고형분 다름 — TDS 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>엑토인 (Ectoine)</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>0.3~2%</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>극한미생물 유래 보호·진정 성분.</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>베타-글루칸 (Beta-Glucan)</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>1~5%(원료액)</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>진정·보습·장벽(보유 원료).</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>귀리추출물</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>콜로이달오트밀 (Colloidal Oatmeal)</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>가려움·건조 진정. 장벽 크림 단골.</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>오트밀분말</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>전분 — 미생물 영양원, 방부 철저</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>디포타슘글리시리제이트 (Dipotassium Glycyrrhizate)</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.5%</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>감초 유래 수용성 진정.</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>카페인 (Caffeine)</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>0.5~3%</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>부기·눈가·두피 제품.</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>커피추출물</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>글라이콜릭애씨드 (Glycolic Acid, AHA)</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>3~10%</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>각질·피부결. pH 3.5~4에서 작동.</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>자외선 민감↑ — AHA 주의문구 표시 대상, 고시 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>락틱애씨드 (Lactic Acid, AHA)</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>2~5%</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>순한 AHA + 보습.</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>pH 관리·주의문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>만델릭애씨드 (Mandelic Acid)</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>2~5%</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>분자 큰 AHA — 민감·지성 각질.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>pH 3.5 내외</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>글루코노락톤 (Gluconolactone, PHA)</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>2~10%</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>가장 순한 각질 케어 + 보습.</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>아젤라익애씨드 (Azelaic Acid)</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>~10%</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>피지·톤 케어.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>용해 어려움. 고농도는 의약품 영역 — 표방·한도 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>벤질알코올 (Benzyl Alcohol)</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>0.5~1%</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>방부+용제. 에코 방부 블렌드 단골.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>고시 한도 확인, 향료 알레르기 성분으로도 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>클로페네신 (Chlorphenesin)</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.3%</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>곰팡이·세균 보조 방부. 페녹시와 병용.</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>고시 0.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>디하이드로아세틱애씨드+벤질알코올 (Geogard 221)</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>0.6~1%</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>에코서트 허용 방부 블렌드.</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>pH ≤6에서 효력</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>소르비탄카프릴레이트 (Sorbitan Caprylate)</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>0.5~1%</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>곰팡이 부스터 — '무방부 표방' 블렌드.</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>단독 방부 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>글리세릴카프릴레이트 (Glyceryl Caprylate)</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>0.3~1%</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>방부·유화 보조. C8 → 세이프.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>단독 방부 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
           <t>항산화</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>아스코빌팔미테이트 (Ascorbyl Palmitate)</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>0.01~0.2%</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>유상 항산화 — 토코페롤과 시너지.</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>팔미트산 에스터 — 소량이라 영향 작음</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>페룰릭애씨드 (Ferulic Acid)</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>비타민C+E 안정·시너지(CE페룰릭).</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>산성에서 용해, 변색</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>레스베라트롤 (Resveratrol)</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>0.1~1%</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>폴리페놀 항산화.</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>레드와인추출물</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>용해 어려움·광불안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>유비퀴논 (Ubiquinone, CoQ10)</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>0.05~0.3%</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>지용성 항산화.</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>수상 제형엔 가용화제 필요(역설계 세럼 교훈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>킬레이트·pH</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>소듐피테이트 (Sodium Phytate)</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>0.05~0.2%</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>쌀겨 유래 천연 킬레이트.</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>킬레이트·pH</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>테트라소듐글루타메이트디아세테이트 (GLDA)</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.2%</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>생분해성 킬레이트(EDTA 대체).</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>소듐피테이트</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>킬레이트·pH</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>아르기닌 (Arginine)</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>0.1~1%</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>아미노산 염기 — 카보머 중화·pH↑.</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>킬레이트·pH</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>트로메타민 (Tromethamine)</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.5%</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>카보머 중화 표준(보유 원료).</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>아르기닌</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>킬레이트·pH</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>락틱애씨드/소듐락테이트 버퍼</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>0.1~1%</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>약산성 고정 버퍼(시트레이트 대안).</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>아크릴레이츠/C10-30알킬아크릴레이트크로스폴리머 (Ultrez 20)</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.5%</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>투명 젤·에멀전 안정. 카보머보다 분산 쉬움.</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>잔탄검</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>중화 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>소듐폴리아크릴레이트 (Sodium Polyacrylate)</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>0.3~1%</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>중화 불필요 즉석 점증.</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>전해질에 약함</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>하이드록시에틸아크릴레이트/소듐아크릴로일디메틸타우레이트코폴리머</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>0.5~2%</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>냉각 유화·점증 겸용 폴리머 — 쉬운 로션.</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>합성 폴리머 포지션</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>셀룰로오스검 (Cellulose Gum, CMC)</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>0.5~2%</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>천연유래 점증, 치약·젤.</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>스클레로튬검 (Sclerotium Gum)</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>0.5~1.5%</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>미끈거림 적은 천연 젤.</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>잔탄검</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>마그네슘알루미늄실리케이트 (Veegum)</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>0.5~2%</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>클레이계 점증·안정(잔탄과 시너지).</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>하이드록시프로필구아 (Hydroxypropyl Guar)</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>0.3~1%</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>세정제 점증·컨디셔닝.</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>가용화</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>PEG-40 하이드로제네이티드캐스터오일</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>향·EO·지용성 활성 가용화 표준(투명 토너).</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>올리브리퀴드</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>향:가용화제 1:3~1:5. PEG — 클린 포지션 상충</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>가용화</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>폴리글리세릴-4 카프레이트 (Polyglyceryl-4 Caprate)</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>1~5%</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>PEG-free 가용화. C10이라 세이프 쪽(보유 원료).</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>가용화력 약함 — 비율↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>가용화</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>PPG-26-부테스-26/PEG-40 하이드로제네이티드캐스터오일</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>1~4%</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>강력 가용화 — 향 많은 미스트.</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>PEG/PPG 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>폴리글리세릴-3 메틸글루코오스디스테아레이트 (Tego Care 450)</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>2~4%</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>PEG-free 비이온 O/W. 가볍고 안정적인 로션·크림.</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>올리벰1000</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>스테아르산 에스터 — 말라세지아 회색지대</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>글리세릴스테아레이트시트레이트 (Glyceryl Stearate Citrate)</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>2~4%</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>음이온 천연유래 O/W. 산뜻한 로션.</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>스테아르산계 회색지대, 공유화제 병용</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>포타슘세틸포스페이트 (Potassium Cetyl Phosphate)</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>0.5~2%</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>보조 유화 — 안정성·내수성↑.</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>pH·전해질 영향 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>BTMS-50 (Behentrimonium Methosulfate &amp; Cetearyl Alcohol)</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>2~6%</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>양이온 유화제 — 헤어 컨디셔너·린스.</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>음이온 계면과 같은 제형에선 침전</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>세틸PEG/PPG-10/1 디메치콘 (W/O 유화제)</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>1~3%</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>실리콘계 W/O — 수분 많은 W/O 크림·선크림.</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>W/O는 전해질(염) 0.5~1% 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>코카미도프로필베타인 (Cocamidopropyl Betaine)</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>5~15%</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>양쪽성 보조 — 거품 안정·자극 완화.</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>코코베타인</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>알레르기 드묾(불순물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>데실글루코사이드 (Decyl Glucoside)</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>5~15%</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>비이온 APG — 순한 세정, 베이비·민감.</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>원료 pH 11~12 — 산으로 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>코코글루코사이드 (Coco-Glucoside)</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>5~15%</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>비이온 APG — 거품 풍부.</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>pH 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>소듐코코일이세티오네이트 (SCI)</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>5~20%</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>순한 음이온 크림 거품 — 샴푸바·클렌징바.</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>용해 어려움(가열)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>소듐라우로일메틸이세티오네이트 (SLMI)</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>5~15%</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>액상 친화 이세티오네이트 — 순하고 풍부한 거품.</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>소듐코코일글루타메이트 (Sodium Cocoyl Glutamate)</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>5~15%</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>아미노산계 약산성 세정 — 얼굴·민감.</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>거품 적음·고가</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>소듐라우로일사코시네이트 (Sodium Lauroyl Sarcosinate)</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>3~10%</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>아미노산계 음이온 — 거품 우수.</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>소듐라우레스설페이트 (SLES)</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>5~15%</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>강한 세정·거품, 저렴 범용.</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>자극·'설페이트 프리' 시장 정서</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>폴리쿼터늄-10 (Polyquaternium-10)</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>0.1~0.5%</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>양이온 컨디셔닝 폴리머 — 샴푸 후 부드러움.</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>양이온 구아</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>음이온과 복합체 — 투명도 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>자외선</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>징크옥사이드 (Zinc Oxide)</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>~25%(고시)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>무기 UVA/UVB 차단, 순함.</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>SPF 표방은 기능성 심사 필요 — 집 제조품 표방 금지. 백탁</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>자외선</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>티타늄디옥사이드 (Titanium Dioxide)</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>~25%(고시)</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>무기 UVB 차단.</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>같음. 백탁</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>자외선</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>에칠헥실메톡시신나메이트 (EHMC)</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>~7.5%(고시)</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>대표 유기 UVB 흡수제(시너메이트류).</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>광분해, 기능성 심사</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>자외선</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>비스-에칠헥실옥시페놀메톡시페닐트리아진 (Tinosorb S)</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>~10%(고시)</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>광안정 광범위 UVA/UVB.</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>유용성, 기능성 심사</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>항산화</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>토코페롤 (Vitamin E)</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
         <is>
           <t>0.1~1%</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>오일·제형 산패 방지(필수). 피부 항산화.</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>자체가 천연</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>과량 시 끈적·알러지 드묾</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="14" t="inlineStr">
         <is>
           <t>항산화</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>로즈마리추출물(올레오레진)/BHT</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>0.05~0.5%</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>오일 산패 지연. 무수·오일 제형 보존기간↑.</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>로즈마리(천연)</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>BHT는 합성 — 천연시 로즈마리</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F36"/>
+  <autoFilter ref="A2:F132"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -1731,29 +4859,29 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>구간(%)</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>결과 · 제형/상품성</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>팁</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>유화제 %(O/W)</t>
         </is>
@@ -1775,7 +4903,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="13" t="n"/>
+      <c r="A4" s="20" t="n"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>2~3%</t>
@@ -1793,7 +4921,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="13" t="n"/>
+      <c r="A5" s="20" t="n"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>4~5%</t>
@@ -1811,7 +4939,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="14" t="n"/>
+      <c r="A6" s="21" t="n"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>6~8%</t>
@@ -1829,83 +4957,83 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>왁스/경화 %(무수 밤)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>5~10%</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>소프트밤·버터. 말랑 떠먹는 제형</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>손 체온에 녹는 질감</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="20" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>10~18%</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>밤·연고. 적당히 단단</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>밀랍/칸데릴라 비율로 미세조정</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>18~25%</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>스틱·립밤. 밀어 올려 바름</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>칸데릴라는 밀랍보다 단단(식물성)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="14" t="n"/>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>25%+</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>데오/고형 스틱. 매우 단단</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>과다 시 끌림·백탁·발림 저하</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>계면활성제 %(세정)</t>
         </is>
@@ -1927,7 +5055,7 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="n"/>
+      <c r="A12" s="20" t="n"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>10~20%</t>
@@ -1945,7 +5073,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="14" t="n"/>
+      <c r="A13" s="21" t="n"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>20~40%</t>
@@ -1963,83 +5091,83 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>점증제 %(잔탄/카보머)</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>잔탄 0.2~0.5%</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>가벼운 점도·유화 안정</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>글리세린 선분산 후 투입(덩어리 방지)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="A15" s="20" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>잔탄 0.5~1%</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>젤~세럼 바디감</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>&gt;0.7% 실뭉침·늘어짐 주의</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="n"/>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="A16" s="20" t="n"/>
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>카보머 0.1~0.3%</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>맑고 가벼운 젤</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>중화 필요(TEA/NaOH)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>카보머 0.3~0.5%</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>탄탄한 투명 젤</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>전해질·저pH·알콜에 무너짐</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>습윤제 %(글리세린)</t>
         </is>
@@ -2061,7 +5189,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="n"/>
+      <c r="A19" s="20" t="n"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
           <t>5~8%</t>
@@ -2079,7 +5207,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="14" t="n"/>
+      <c r="A20" s="21" t="n"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>8%+</t>
@@ -2097,83 +5225,83 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>유상(오일) %</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>토너·미스트(수상 85~95%)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>가용화제로 소량 오일/EO만</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>5~15%</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>로션. 가벼운 보습막</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>유화제 3~5% 동반</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="A23" s="20" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>15~30%</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>크림. 리치 보습</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>유화·점도 설계 중요</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>무수(100%)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>오일·밤. 방부 불필요</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>물 유입 금지·항산화 필수</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>향/에센셜오일 %</t>
         </is>
@@ -2195,7 +5323,7 @@
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="13" t="n"/>
+      <c r="A26" s="20" t="n"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>0.5~1%</t>
@@ -2213,7 +5341,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="14" t="n"/>
+      <c r="A27" s="21" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>&gt;1%</t>
